--- a/nodes_source_analyses/molecules/molecules/molecules_production_fischer_tropsch_synthetic_dispatchable_co2.xlsx
+++ b/nodes_source_analyses/molecules/molecules/molecules_production_fischer_tropsch_synthetic_dispatchable_co2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10525"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mathijsbijkerk/Github/etdataset/nodes_source_analyses/molecules/molecules/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyradehaan/github/etdataset/nodes_source_analyses/molecules/molecules/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA6F81F-E479-EF47-A501-C22D2B9696F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7E2AA3-76FC-8D4B-8D86-DFB1582B0353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" tabRatio="762" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4900" yWindow="-21600" windowWidth="38400" windowHeight="21600" tabRatio="762" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet" sheetId="14" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <definedName name="Wp_to_kWp">#REF!</definedName>
     <definedName name="WP_to_MWp">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="187">
   <si>
     <t>Source</t>
   </si>
@@ -599,21 +599,12 @@
     <t>t CO2/t FT liquids</t>
   </si>
   <si>
-    <t>CO2 consumption per t kerosene</t>
-  </si>
-  <si>
-    <t>t CO2/t kerosene</t>
-  </si>
-  <si>
     <t>LHV kerosene</t>
   </si>
   <si>
     <t>MJ/kg</t>
   </si>
   <si>
-    <t>CO2 consumption per MJ kerosene</t>
-  </si>
-  <si>
     <t>kg CO2/MJ kerosene</t>
   </si>
   <si>
@@ -630,6 +621,33 @@
   </si>
   <si>
     <t>DEA</t>
+  </si>
+  <si>
+    <t>assumption: all output is kerosene</t>
+  </si>
+  <si>
+    <t>CO2 consumption per MJ product</t>
+  </si>
+  <si>
+    <t>kg CO2/MJ FT products</t>
+  </si>
+  <si>
+    <t>check with emissions factors (EF) to confirm required input of CO2 is higher than EF</t>
+  </si>
+  <si>
+    <t>Emissions factor kerosene</t>
+  </si>
+  <si>
+    <t>copied from carriers.csv nl2023</t>
+  </si>
+  <si>
+    <t>Emission factor gasoline</t>
+  </si>
+  <si>
+    <t>kg CO2/MJ gasoline</t>
+  </si>
+  <si>
+    <t>from_energy.conversion.gasoline</t>
   </si>
 </sst>
 </file>
@@ -645,12 +663,19 @@
     <numFmt numFmtId="168" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="169" formatCode="[$-413]mmm\-yy;@"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="41">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Lettertype hoofdtekst"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1215,842 +1240,838 @@
   </borders>
   <cellStyleXfs count="500">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="33" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="32" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="29" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="33" fillId="2" borderId="0" xfId="498" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="28" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="32" fillId="2" borderId="0" xfId="498" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="27" fillId="2" borderId="0" xfId="498" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="2" borderId="0" xfId="498" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="35" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="34" fillId="2" borderId="0" xfId="496" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="9" fontId="33" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="34" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="34" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="29" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="34" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="33" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="9" fontId="32" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="32" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="26" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="33" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="17" fillId="2" borderId="0" xfId="499" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="17" fillId="2" borderId="0" xfId="499" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="497" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="17" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="0" xfId="499" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="18" fillId="2" borderId="0" xfId="499" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="0" xfId="497" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="497" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="497" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" xfId="497" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="2" xfId="497" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="500">
     <cellStyle name="Comma" xfId="499" builtinId="3"/>
@@ -3067,12 +3088,12 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.5" style="25" customWidth="1"/>
-    <col min="2" max="2" width="11.5" style="17" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="17" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="17"/>
+    <col min="1" max="1" width="3.42578125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="38.42578125" style="17" customWidth="1"/>
+    <col min="4" max="16384" width="10.85546875" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="23" customFormat="1">
@@ -3098,7 +3119,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3244,45 +3265,45 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A2:J22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
+  <dimension ref="A2:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="3.5" style="27" customWidth="1"/>
-    <col min="3" max="3" width="51.5" style="27" customWidth="1"/>
-    <col min="4" max="5" width="14.6640625" style="27" customWidth="1"/>
-    <col min="6" max="6" width="4.5" style="27" customWidth="1"/>
-    <col min="7" max="7" width="49.5" style="27" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" style="27" customWidth="1"/>
-    <col min="9" max="9" width="42.5" style="27" customWidth="1"/>
-    <col min="10" max="10" width="5.5" style="27" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="27"/>
+    <col min="1" max="2" width="3.42578125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" style="27" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="27" customWidth="1"/>
+    <col min="6" max="6" width="4.42578125" style="27" customWidth="1"/>
+    <col min="7" max="7" width="49.42578125" style="27" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" style="27" customWidth="1"/>
+    <col min="9" max="9" width="42.42578125" style="27" customWidth="1"/>
+    <col min="10" max="10" width="5.42578125" style="27" customWidth="1"/>
+    <col min="11" max="16384" width="10.85546875" style="27"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10">
-      <c r="B2" s="163" t="s">
+      <c r="B2" s="159" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="165"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="161"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="B3" s="166"/>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="168"/>
+      <c r="B3" s="162"/>
+      <c r="C3" s="163"/>
+      <c r="D3" s="163"/>
+      <c r="E3" s="164"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="166"/>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="168"/>
+      <c r="B4" s="162"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="163"/>
+      <c r="E4" s="164"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="B5" s="169"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="171"/>
+      <c r="B5" s="165"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="167"/>
     </row>
     <row r="7" spans="1:10" ht="17" thickBot="1"/>
     <row r="8" spans="1:10">
@@ -3326,48 +3347,59 @@
       <c r="A11" s="64"/>
       <c r="B11" s="65"/>
       <c r="C11" s="155" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="162">
-        <f>ROUND(Notes!F49,5)</f>
-        <v>6.7790000000000003E-2</v>
+      <c r="E11" s="156">
+        <f>ROUND(Notes!$F$48,5)</f>
+        <v>9.0380000000000002E-2</v>
       </c>
       <c r="F11" s="63"/>
       <c r="G11" s="155" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H11" s="63"/>
-      <c r="I11" s="176" t="s">
-        <v>180</v>
+      <c r="I11" s="157" t="s">
+        <v>177</v>
       </c>
       <c r="J11" s="66"/>
     </row>
     <row r="12" spans="1:10" ht="17" thickBot="1">
       <c r="A12" s="64"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="69"/>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="B12" s="65"/>
+      <c r="C12" s="172" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="156">
+        <f>ROUND(Notes!$F$48,5)</f>
+        <v>9.0380000000000002E-2</v>
+      </c>
+      <c r="F12" s="63"/>
+      <c r="G12" s="155" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" s="63"/>
+      <c r="I12" s="157" t="s">
+        <v>177</v>
+      </c>
+      <c r="J12" s="66"/>
+    </row>
+    <row r="13" spans="1:10" ht="17" thickBot="1">
       <c r="A13" s="64"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="64"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="69"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="64"/>
@@ -3396,6 +3428,8 @@
     <row r="16" spans="1:10">
       <c r="A16" s="64"/>
       <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
       <c r="E16" s="64"/>
       <c r="F16" s="64"/>
       <c r="G16" s="64"/>
@@ -3406,8 +3440,6 @@
     <row r="17" spans="1:10">
       <c r="A17" s="64"/>
       <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
       <c r="E17" s="64"/>
       <c r="F17" s="64"/>
       <c r="G17" s="64"/>
@@ -3453,9 +3485,21 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="64"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="64"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3472,19 +3516,19 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="B1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.1640625" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.5" style="30" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" style="30" customWidth="1"/>
-    <col min="3" max="3" width="24.5" style="30" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" style="30" customWidth="1"/>
-    <col min="5" max="5" width="6.1640625" style="30" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" style="30" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="30" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" style="30" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" style="30" customWidth="1"/>
+    <col min="4" max="4" width="32.85546875" style="30" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" style="30" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" style="30" customWidth="1"/>
     <col min="7" max="7" width="78" style="30" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="34" customWidth="1"/>
-    <col min="9" max="9" width="31.5" style="34" customWidth="1"/>
-    <col min="10" max="10" width="98.5" style="30" customWidth="1"/>
-    <col min="11" max="16384" width="33.1640625" style="30"/>
+    <col min="8" max="8" width="12.42578125" style="34" customWidth="1"/>
+    <col min="9" max="9" width="31.42578125" style="34" customWidth="1"/>
+    <col min="10" max="10" width="98.42578125" style="30" customWidth="1"/>
+    <col min="11" max="16384" width="33.140625" style="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="17" thickBot="1"/>
@@ -3614,7 +3658,7 @@
       <c r="B13" s="33"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I7" r:id="rId1" xr:uid="{877979D8-94D4-4246-B8F7-7FF5F6E32CF4}"/>
     <hyperlink ref="I8" r:id="rId2" xr:uid="{06CFC551-C46B-2F44-A4BE-28617D395B80}"/>
@@ -3630,18 +3674,18 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Z131"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="3.5" style="37" customWidth="1"/>
-    <col min="3" max="3" width="18.5" style="37" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" style="37" customWidth="1"/>
-    <col min="5" max="5" width="23.6640625" style="37" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="3.42578125" style="37" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="37" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" style="37" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" style="37" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="37" customWidth="1"/>
-    <col min="7" max="7" width="23.1640625" style="37" customWidth="1"/>
-    <col min="8" max="13" width="10.83203125" style="37"/>
-    <col min="14" max="15" width="15.6640625" style="37" customWidth="1"/>
-    <col min="16" max="16" width="24.5" style="37" customWidth="1"/>
-    <col min="17" max="16384" width="10.83203125" style="37"/>
+    <col min="7" max="7" width="23.140625" style="37" customWidth="1"/>
+    <col min="8" max="13" width="10.85546875" style="37"/>
+    <col min="14" max="15" width="15.7109375" style="37" customWidth="1"/>
+    <col min="16" max="16" width="24.42578125" style="37" customWidth="1"/>
+    <col min="17" max="16384" width="10.85546875" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="17" thickBot="1"/>
@@ -3726,18 +3770,18 @@
         <v>50</v>
       </c>
       <c r="P6" s="75"/>
-      <c r="Q6" s="174" t="s">
+      <c r="Q6" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="R6" s="175"/>
-      <c r="S6" s="175"/>
-      <c r="T6" s="175"/>
-      <c r="U6" s="175"/>
-      <c r="V6" s="175"/>
-      <c r="W6" s="175"/>
-      <c r="X6" s="175"/>
-      <c r="Y6" s="175"/>
-      <c r="Z6" s="175"/>
+      <c r="R6" s="171"/>
+      <c r="S6" s="171"/>
+      <c r="T6" s="171"/>
+      <c r="U6" s="171"/>
+      <c r="V6" s="171"/>
+      <c r="W6" s="171"/>
+      <c r="X6" s="171"/>
+      <c r="Y6" s="171"/>
+      <c r="Z6" s="171"/>
     </row>
     <row r="7" spans="1:26" ht="17" customHeight="1">
       <c r="A7" s="41"/>
@@ -3747,7 +3791,7 @@
         <v>42</v>
       </c>
       <c r="F7" s="86">
-        <f>F55</f>
+        <f>F56</f>
         <v>8000</v>
       </c>
       <c r="G7" s="37" t="s">
@@ -3798,7 +3842,7 @@
         <v>43</v>
       </c>
       <c r="F8" s="86">
-        <f>F56</f>
+        <f>F57</f>
         <v>25</v>
       </c>
       <c r="G8" s="37" t="s">
@@ -3846,7 +3890,7 @@
         <v>147</v>
       </c>
       <c r="F9" s="86">
-        <f>F57</f>
+        <f>F58</f>
         <v>2</v>
       </c>
       <c r="G9" s="37" t="s">
@@ -3876,7 +3920,7 @@
         <v>148</v>
       </c>
       <c r="F10" s="72">
-        <f>F58</f>
+        <f>F59</f>
         <v>0.94230769230769229</v>
       </c>
       <c r="O10" s="81" t="s">
@@ -3939,7 +3983,7 @@
         <v>40</v>
       </c>
       <c r="F12" s="150">
-        <f>F60</f>
+        <f>F61</f>
         <v>871988000</v>
       </c>
       <c r="G12" s="37" t="s">
@@ -3987,7 +4031,7 @@
         <v>135</v>
       </c>
       <c r="F13" s="151">
-        <f>F61</f>
+        <f>F62</f>
         <v>2214849.5199999996</v>
       </c>
       <c r="G13" s="37" t="s">
@@ -4015,7 +4059,7 @@
         <v>137</v>
       </c>
       <c r="F14" s="72">
-        <f>F63</f>
+        <f>F64</f>
         <v>91.558739999999986</v>
       </c>
       <c r="G14" s="37" t="s">
@@ -5036,7 +5080,7 @@
       <c r="Y43" s="83"/>
       <c r="Z43" s="83"/>
     </row>
-    <row r="44" spans="1:26" ht="17" thickBot="1">
+    <row r="44" spans="1:26">
       <c r="O44" s="144"/>
       <c r="P44" s="144" t="s">
         <v>110</v>
@@ -5053,14 +5097,9 @@
       <c r="Z44" s="83"/>
     </row>
     <row r="45" spans="1:26">
-      <c r="E45" s="156" t="s">
+      <c r="E45" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="39"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="40"/>
       <c r="O45" s="144"/>
       <c r="P45" s="144" t="s">
         <v>111</v>
@@ -5077,7 +5116,7 @@
       <c r="Z45" s="83"/>
     </row>
     <row r="46" spans="1:26">
-      <c r="E46" s="43" t="s">
+      <c r="E46" s="37" t="s">
         <v>168</v>
       </c>
       <c r="F46" s="37">
@@ -5087,7 +5126,9 @@
       <c r="G46" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="J46" s="157"/>
+      <c r="H46" s="37" t="s">
+        <v>178</v>
+      </c>
       <c r="O46" s="144"/>
       <c r="P46" s="144" t="s">
         <v>112</v>
@@ -5104,17 +5145,18 @@
       <c r="Z46" s="83"/>
     </row>
     <row r="47" spans="1:26">
-      <c r="E47" s="43" t="s">
+      <c r="E47" s="37" t="s">
         <v>170</v>
       </c>
       <c r="F47" s="37">
-        <f>F46*H39/H42</f>
-        <v>2.9249999999999998</v>
+        <v>43.15</v>
       </c>
       <c r="G47" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="J47" s="157"/>
+      <c r="H47" s="37" t="s">
+        <v>173</v>
+      </c>
       <c r="O47" s="144"/>
       <c r="P47" s="144" t="s">
         <v>113</v>
@@ -5131,19 +5173,19 @@
       <c r="Z47" s="83"/>
     </row>
     <row r="48" spans="1:26">
-      <c r="E48" s="43" t="s">
-        <v>172</v>
-      </c>
-      <c r="F48" s="37">
-        <v>43.15</v>
+      <c r="E48" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F48" s="158">
+        <f>F46/F47</f>
+        <v>9.0382387022016217E-2</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="J48" s="157"/>
+        <v>181</v>
+      </c>
       <c r="O48" s="144"/>
       <c r="P48" s="144" t="s">
         <v>114</v>
@@ -5159,20 +5201,19 @@
       <c r="Y48" s="83"/>
       <c r="Z48" s="83"/>
     </row>
-    <row r="49" spans="5:26" ht="17" thickBot="1">
-      <c r="E49" s="158" t="s">
-        <v>174</v>
-      </c>
-      <c r="F49" s="159">
-        <f>F47/F48</f>
-        <v>6.7786790266512159E-2</v>
-      </c>
-      <c r="G49" s="160" t="s">
-        <v>175</v>
-      </c>
-      <c r="H49" s="160"/>
-      <c r="I49" s="160"/>
-      <c r="J49" s="161"/>
+    <row r="49" spans="5:26">
+      <c r="E49" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="F49" s="37">
+        <v>7.1499999999999994E-2</v>
+      </c>
+      <c r="G49" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="H49" s="37" t="s">
+        <v>183</v>
+      </c>
       <c r="O49" s="144"/>
       <c r="P49" s="144" t="s">
         <v>115</v>
@@ -5189,6 +5230,18 @@
       <c r="Z49" s="83"/>
     </row>
     <row r="50" spans="5:26">
+      <c r="E50" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="37">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="G50" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="H50" s="37" t="s">
+        <v>183</v>
+      </c>
       <c r="O50" s="144"/>
       <c r="P50" s="144" t="s">
         <v>116</v>
@@ -5221,9 +5274,6 @@
       <c r="Z51" s="83"/>
     </row>
     <row r="52" spans="5:26">
-      <c r="E52" s="41" t="s">
-        <v>126</v>
-      </c>
       <c r="O52" s="144"/>
       <c r="P52" s="144" t="s">
         <v>118</v>
@@ -5240,15 +5290,8 @@
       <c r="Z52" s="83"/>
     </row>
     <row r="53" spans="5:26">
-      <c r="E53" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="F53" s="37">
-        <f>S26*10^3</f>
-        <v>75000</v>
-      </c>
-      <c r="G53" s="37" t="s">
-        <v>128</v>
+      <c r="E53" s="41" t="s">
+        <v>126</v>
       </c>
       <c r="O53" s="144"/>
       <c r="P53" s="144" t="s">
@@ -5267,14 +5310,14 @@
     </row>
     <row r="54" spans="5:26">
       <c r="E54" s="37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F54" s="37">
-        <f>R12</f>
-        <v>20.5</v>
+        <f>S26*10^3</f>
+        <v>75000</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="O54" s="144"/>
       <c r="P54" s="144" t="s">
@@ -5293,79 +5336,79 @@
     </row>
     <row r="55" spans="5:26">
       <c r="E55" s="37" t="s">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="F55" s="37">
-        <v>8000</v>
+        <f>R12</f>
+        <v>20.5</v>
       </c>
       <c r="G55" s="37" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="5:26">
       <c r="E56" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" s="37">
+        <v>8000</v>
+      </c>
+      <c r="G56" s="37" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="5:26">
+      <c r="E57" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="F56" s="37">
+      <c r="F57" s="37">
         <f>Q22</f>
         <v>25</v>
       </c>
-      <c r="G56" s="37" t="s">
+      <c r="G57" s="37" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="5:26">
-      <c r="E57" s="37" t="s">
+    <row r="58" spans="5:26">
+      <c r="E58" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="F57" s="86">
+      <c r="F58" s="86">
         <f>Q23</f>
         <v>2</v>
       </c>
-      <c r="G57" s="37" t="s">
+      <c r="G58" s="37" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="58" spans="5:26">
-      <c r="E58" s="37" t="s">
+    <row r="59" spans="5:26">
+      <c r="E59" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="F58" s="72">
+      <c r="F59" s="72">
         <f>1-Q21/52</f>
         <v>0.94230769230769229</v>
       </c>
     </row>
-    <row r="60" spans="5:26">
-      <c r="E60" s="37" t="s">
+    <row r="61" spans="5:26">
+      <c r="E61" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="F60" s="149">
+      <c r="F61" s="149">
         <f>R25*R12*Q22*10^6</f>
         <v>871988000</v>
       </c>
-      <c r="G60" s="37" t="s">
+      <c r="G61" s="37" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="61" spans="5:26">
-      <c r="E61" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="F61" s="149">
-        <f>R28*R12*F55</f>
-        <v>2214849.5199999996</v>
-      </c>
-      <c r="G61" s="37" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="62" spans="5:26">
       <c r="E62" s="37" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F62" s="149">
-        <f>R29*R12*F55</f>
-        <v>732469.91999999993</v>
+        <f>R28*R12*F56</f>
+        <v>2214849.5199999996</v>
       </c>
       <c r="G62" s="37" t="s">
         <v>136</v>
@@ -5375,11 +5418,23 @@
       <c r="E63" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="F63" s="72">
-        <f>F62/F55</f>
+      <c r="F63" s="149">
+        <f>R29*R12*F56</f>
+        <v>732469.91999999993</v>
+      </c>
+      <c r="G63" s="37" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="5:26">
+      <c r="E64" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="F64" s="72">
+        <f>F63/F56</f>
         <v>91.558739999999986</v>
       </c>
-      <c r="G63" s="37" t="s">
+      <c r="G64" s="37" t="s">
         <v>138</v>
       </c>
     </row>
@@ -5387,17 +5442,17 @@
       <c r="E79" s="41"/>
       <c r="N79" s="93"/>
       <c r="O79" s="94"/>
-      <c r="P79" s="172"/>
-      <c r="Q79" s="173"/>
-      <c r="R79" s="173"/>
-      <c r="S79" s="173"/>
-      <c r="T79" s="173"/>
-      <c r="U79" s="173"/>
-      <c r="V79" s="173"/>
-      <c r="W79" s="173"/>
-      <c r="X79" s="173"/>
-      <c r="Y79" s="173"/>
-      <c r="Z79" s="173"/>
+      <c r="P79" s="168"/>
+      <c r="Q79" s="169"/>
+      <c r="R79" s="169"/>
+      <c r="S79" s="169"/>
+      <c r="T79" s="169"/>
+      <c r="U79" s="169"/>
+      <c r="V79" s="169"/>
+      <c r="W79" s="169"/>
+      <c r="X79" s="169"/>
+      <c r="Y79" s="169"/>
+      <c r="Z79" s="169"/>
     </row>
     <row r="80" spans="5:26">
       <c r="N80" s="94"/>
